--- a/2026학년도 신입생 최종 모집결과(대동대학교)-입력요청정원외.xlsx
+++ b/2026학년도 신입생 최종 모집결과(대동대학교)-입력요청정원외.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prowiz\Desktop\Temp\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4450F6CD-4BCC-431D-8C8D-C50F545A6AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6D6A40-0443-42D5-81EE-E0EAB1A3328D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B447207A-A5D3-4CA2-A129-A3AF98236A0A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{B447207A-A5D3-4CA2-A129-A3AF98236A0A}"/>
   </bookViews>
   <sheets>
     <sheet name="정원 외 모집결과 최종" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="60">
   <si>
     <t>모집단위</t>
   </si>
@@ -87,9 +87,6 @@
     <t>0</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>야간</t>
   </si>
   <si>
@@ -105,24 +102,12 @@
     <t>14</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>응급구조과</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>호텔조리&amp;베이커리과</t>
   </si>
   <si>
@@ -130,9 +115,6 @@
   </si>
   <si>
     <t>18</t>
-  </si>
-  <si>
-    <t>194</t>
   </si>
   <si>
     <t>호텔소믈리에&amp;바리스타과</t>
@@ -178,12 +160,6 @@
     <t>장애인 등 대상자(4호)</t>
   </si>
   <si>
-    <t>전문대학 이상 졸업자(8호)</t>
-  </si>
-  <si>
-    <t>만학도 및 성인재직자(12호)</t>
-  </si>
-  <si>
     <t>기회균형 선발</t>
   </si>
   <si>
@@ -193,76 +169,10 @@
     <t>다자녀 가정 및 다문화가족(제주도지역 한정)</t>
   </si>
   <si>
-    <t>입학정원 2%이내</t>
-  </si>
-  <si>
-    <t>북한이탈주민</t>
-  </si>
-  <si>
-    <t>순수외국인(6호)</t>
-  </si>
-  <si>
     <t>전과정이수자(7호)</t>
   </si>
   <si>
-    <t>전문대졸</t>
-  </si>
-  <si>
-    <t>대졸(2년이상 수료자)</t>
-  </si>
-  <si>
-    <t>대졸(4년 졸업자)</t>
-  </si>
-  <si>
-    <t>농어촌학생(가목)</t>
-  </si>
-  <si>
     <t>특성화고 등을 졸업한 재직자(다목)</t>
-  </si>
-  <si>
-    <t>기초수급권자/차상위계층/한부모가족 지원대상자(라목)</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>68</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>143</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>623</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>5.51</t>
-  </si>
-  <si>
-    <t>92.92</t>
   </si>
   <si>
     <t>모집인원</t>
@@ -270,6 +180,201 @@
   </si>
   <si>
     <t>등록인원</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>농어촌전형</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>만학도</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대학졸업자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년제</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년이상</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수료자</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>4년제</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(4</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>졸업자</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2년제졸업자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>기초생활수급자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>순수외국인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>북한이탈주민</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재외국민</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>및외국인</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -280,7 +385,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.0#####################"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="12">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -341,6 +446,29 @@
       <color rgb="FFFFFFFF"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial Unicode MS"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -479,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -517,13 +645,13 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -532,7 +660,25 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -541,10 +687,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -929,104 +1072,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:61">
-      <c r="A1" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="14"/>
-      <c r="S1" s="14"/>
-      <c r="T1" s="14"/>
-      <c r="U1" s="14"/>
-      <c r="V1" s="14"/>
-      <c r="W1" s="14"/>
-      <c r="X1" s="14"/>
-      <c r="Y1" s="14"/>
-      <c r="Z1" s="14"/>
-      <c r="AA1" s="14"/>
-      <c r="AB1" s="14"/>
-      <c r="AC1" s="14"/>
-      <c r="AD1" s="14"/>
-      <c r="AE1" s="14"/>
-      <c r="AF1" s="14"/>
-      <c r="AG1" s="14"/>
-      <c r="AH1" s="14"/>
-      <c r="AI1" s="14"/>
-      <c r="AJ1" s="14"/>
-      <c r="AK1" s="14"/>
-      <c r="AL1" s="14"/>
-      <c r="AM1" s="14"/>
-      <c r="AN1" s="14"/>
-      <c r="AO1" s="14"/>
-      <c r="AP1" s="14"/>
-      <c r="AQ1" s="14"/>
-      <c r="AR1" s="14"/>
-      <c r="AS1" s="14"/>
-      <c r="AT1" s="14"/>
-      <c r="AU1" s="14"/>
-      <c r="AV1" s="14"/>
-      <c r="AW1" s="14"/>
-      <c r="AX1" s="14"/>
-      <c r="AY1" s="14"/>
-      <c r="AZ1" s="14"/>
-      <c r="BA1" s="14"/>
-      <c r="BB1" s="14"/>
-      <c r="BC1" s="14"/>
-      <c r="BD1" s="13" t="s">
+      <c r="F1" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="27"/>
+      <c r="Y1" s="27"/>
+      <c r="Z1" s="27"/>
+      <c r="AA1" s="27"/>
+      <c r="AB1" s="27"/>
+      <c r="AC1" s="27"/>
+      <c r="AD1" s="27"/>
+      <c r="AE1" s="27"/>
+      <c r="AF1" s="27"/>
+      <c r="AG1" s="27"/>
+      <c r="AH1" s="27"/>
+      <c r="AI1" s="27"/>
+      <c r="AJ1" s="27"/>
+      <c r="AK1" s="27"/>
+      <c r="AL1" s="27"/>
+      <c r="AM1" s="27"/>
+      <c r="AN1" s="27"/>
+      <c r="AO1" s="27"/>
+      <c r="AP1" s="27"/>
+      <c r="AQ1" s="27"/>
+      <c r="AR1" s="27"/>
+      <c r="AS1" s="27"/>
+      <c r="AT1" s="27"/>
+      <c r="AU1" s="27"/>
+      <c r="AV1" s="27"/>
+      <c r="AW1" s="27"/>
+      <c r="AX1" s="27"/>
+      <c r="AY1" s="27"/>
+      <c r="AZ1" s="27"/>
+      <c r="BA1" s="27"/>
+      <c r="BB1" s="27"/>
+      <c r="BC1" s="27"/>
+      <c r="BD1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="BE1" s="13"/>
-      <c r="BF1" s="13"/>
-      <c r="BG1" s="13"/>
-      <c r="BH1" s="13"/>
-      <c r="BI1" s="15" t="s">
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15"/>
+      <c r="BG1" s="15"/>
+      <c r="BH1" s="15"/>
+      <c r="BI1" s="18" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:61">
-      <c r="A2" s="20"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
       <c r="F2" s="16" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="17" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K2" s="17"/>
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" s="16" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="O2" s="16"/>
       <c r="P2" s="16"/>
@@ -1034,13 +1177,13 @@
       <c r="R2" s="16"/>
       <c r="S2" s="16"/>
       <c r="T2" s="17" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="U2" s="17"/>
       <c r="V2" s="17"/>
       <c r="W2" s="17"/>
-      <c r="X2" s="16" t="s">
-        <v>49</v>
+      <c r="X2" s="21" t="s">
+        <v>52</v>
       </c>
       <c r="Y2" s="16"/>
       <c r="Z2" s="16"/>
@@ -1049,14 +1192,14 @@
       <c r="AC2" s="16"/>
       <c r="AD2" s="16"/>
       <c r="AE2" s="16"/>
-      <c r="AF2" s="17" t="s">
-        <v>50</v>
+      <c r="AF2" s="19" t="s">
+        <v>51</v>
       </c>
       <c r="AG2" s="17"/>
       <c r="AH2" s="17"/>
       <c r="AI2" s="17"/>
       <c r="AJ2" s="16" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="AK2" s="16"/>
       <c r="AL2" s="16"/>
@@ -1070,38 +1213,38 @@
       <c r="AT2" s="16"/>
       <c r="AU2" s="16"/>
       <c r="AV2" s="17" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="AW2" s="17"/>
       <c r="AX2" s="17"/>
       <c r="AY2" s="17"/>
       <c r="AZ2" s="16" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="BA2" s="16"/>
       <c r="BB2" s="16"/>
       <c r="BC2" s="16"/>
-      <c r="BD2" s="13"/>
-      <c r="BE2" s="13"/>
-      <c r="BF2" s="13"/>
-      <c r="BG2" s="13"/>
-      <c r="BH2" s="13"/>
-      <c r="BI2" s="15"/>
+      <c r="BD2" s="15"/>
+      <c r="BE2" s="15"/>
+      <c r="BF2" s="15"/>
+      <c r="BG2" s="15"/>
+      <c r="BH2" s="15"/>
+      <c r="BI2" s="18"/>
     </row>
     <row r="3" spans="1:61">
-      <c r="A3" s="20"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="16" t="s">
-        <v>54</v>
+      <c r="A3" s="26"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="24" t="s">
+        <v>59</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
       <c r="I3" s="16"/>
-      <c r="J3" s="17" t="s">
-        <v>55</v>
+      <c r="J3" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
@@ -1112,12 +1255,12 @@
       <c r="O3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="16" t="s">
-        <v>56</v>
+      <c r="P3" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="Q3" s="16"/>
       <c r="R3" s="16" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="S3" s="16"/>
       <c r="T3" s="17"/>
@@ -1130,36 +1273,36 @@
       <c r="Y3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="Z3" s="16" t="s">
-        <v>58</v>
+      <c r="Z3" s="20" t="s">
+        <v>55</v>
       </c>
       <c r="AA3" s="16"/>
-      <c r="AB3" s="16" t="s">
-        <v>59</v>
+      <c r="AB3" s="23" t="s">
+        <v>53</v>
       </c>
       <c r="AC3" s="16"/>
-      <c r="AD3" s="16" t="s">
-        <v>60</v>
+      <c r="AD3" s="24" t="s">
+        <v>54</v>
       </c>
       <c r="AE3" s="16"/>
       <c r="AF3" s="17"/>
       <c r="AG3" s="17"/>
       <c r="AH3" s="17"/>
       <c r="AI3" s="17"/>
-      <c r="AJ3" s="16" t="s">
-        <v>61</v>
+      <c r="AJ3" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="AK3" s="16"/>
       <c r="AL3" s="16"/>
       <c r="AM3" s="16"/>
       <c r="AN3" s="17" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="AO3" s="17"/>
       <c r="AP3" s="17"/>
       <c r="AQ3" s="17"/>
-      <c r="AR3" s="16" t="s">
-        <v>63</v>
+      <c r="AR3" s="20" t="s">
+        <v>56</v>
       </c>
       <c r="AS3" s="16"/>
       <c r="AT3" s="16"/>
@@ -1172,24 +1315,24 @@
       <c r="BA3" s="16"/>
       <c r="BB3" s="16"/>
       <c r="BC3" s="16"/>
-      <c r="BD3" s="13"/>
-      <c r="BE3" s="13"/>
-      <c r="BF3" s="13"/>
-      <c r="BG3" s="13"/>
-      <c r="BH3" s="13"/>
-      <c r="BI3" s="15"/>
+      <c r="BD3" s="15"/>
+      <c r="BE3" s="15"/>
+      <c r="BF3" s="15"/>
+      <c r="BG3" s="15"/>
+      <c r="BH3" s="15"/>
+      <c r="BI3" s="18"/>
     </row>
     <row r="4" spans="1:61" ht="24">
-      <c r="A4" s="20"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>79</v>
+      <c r="A4" s="26"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>49</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>7</v>
@@ -1350,7 +1493,7 @@
       <c r="BH4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="BI4" s="15"/>
+      <c r="BI4" s="18"/>
     </row>
     <row r="5" spans="1:61">
       <c r="A5" s="4" t="s">
@@ -1430,7 +1573,7 @@
       <c r="B6" s="11"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>18</v>
@@ -1495,16 +1638,16 @@
     <row r="7" spans="1:61">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="7"/>
@@ -1568,7 +1711,7 @@
       <c r="B8" s="11"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>18</v>
@@ -1633,16 +1776,16 @@
     <row r="9" spans="1:61">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="7"/>
@@ -1706,7 +1849,7 @@
       <c r="B10" s="11"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>18</v>
@@ -1771,16 +1914,16 @@
     <row r="11" spans="1:61">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7"/>
@@ -1844,7 +1987,7 @@
       <c r="B12" s="11"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>18</v>
@@ -1909,16 +2052,16 @@
     <row r="13" spans="1:61">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7"/>
@@ -1982,7 +2125,7 @@
       <c r="B14" s="11"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>18</v>
@@ -2047,16 +2190,16 @@
     <row r="15" spans="1:61">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="7"/>
@@ -2120,7 +2263,7 @@
       <c r="B16" s="11"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>18</v>
@@ -2184,19 +2327,19 @@
     </row>
     <row r="17" spans="1:61">
       <c r="A17" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="7"/>
@@ -2260,7 +2403,7 @@
       <c r="B18" s="11"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>18</v>
@@ -2324,19 +2467,19 @@
     </row>
     <row r="19" spans="1:61">
       <c r="A19" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="7"/>
@@ -2400,7 +2543,7 @@
       <c r="B20" s="11"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>18</v>
@@ -2464,19 +2607,19 @@
     </row>
     <row r="21" spans="1:61">
       <c r="A21" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="7"/>
@@ -2540,7 +2683,7 @@
       <c r="B22" s="11"/>
       <c r="C22" s="6"/>
       <c r="D22" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>18</v>
@@ -2603,181 +2746,69 @@
       <c r="BI22" s="10"/>
     </row>
     <row r="23" spans="1:61">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="M23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="O23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="P23" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="R23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="S23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="T23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="V23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="W23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="X23" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y23" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z23" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA23" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="AB23" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="AC23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD23" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="AE23" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="AF23" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="AG23" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH23" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="AI23" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ23" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK23" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL23" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="AM23" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="AN23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AO23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AP23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AQ23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AR23" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="AS23" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="AT23" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="AU23" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AV23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AW23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AX23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AY23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="AZ23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="BA23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="BB23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC23" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="BD23" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="BE23" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="BF23" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG23" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="BH23" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="BI23" s="12" t="s">
-        <v>28</v>
-      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="12"/>
+      <c r="AA23" s="12"/>
+      <c r="AB23" s="12"/>
+      <c r="AC23" s="12"/>
+      <c r="AD23" s="12"/>
+      <c r="AE23" s="12"/>
+      <c r="AF23" s="12"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="12"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+      <c r="BI23" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -2789,30 +2820,30 @@
     <mergeCell ref="Y3:Y4"/>
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B1:B4"/>
-    <mergeCell ref="BI1:BI4"/>
+    <mergeCell ref="C1:C4"/>
+    <mergeCell ref="D1:D4"/>
+    <mergeCell ref="E1:E4"/>
+    <mergeCell ref="F1:BC1"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="N2:S2"/>
     <mergeCell ref="T2:W3"/>
-    <mergeCell ref="X2:AE2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="BD1:BH3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="BI1:BI4"/>
     <mergeCell ref="AF2:AI3"/>
     <mergeCell ref="AJ2:AU2"/>
     <mergeCell ref="AR3:AU3"/>
     <mergeCell ref="AV2:AY3"/>
     <mergeCell ref="AZ2:BC3"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="C1:C4"/>
-    <mergeCell ref="D1:D4"/>
-    <mergeCell ref="E1:E4"/>
-    <mergeCell ref="F1:BC1"/>
-    <mergeCell ref="BD1:BH3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="AN3:AQ3"/>
+    <mergeCell ref="X2:AE2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
